--- a/Plan De Pruebas Entrega 1 Estructuras de datos.xlsx
+++ b/Plan De Pruebas Entrega 1 Estructuras de datos.xlsx
@@ -5,15 +5,23 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lckyz007/Documents/Estructuras De Datos/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lckyz007/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0D214438-8BAA-3242-867A-F11438266557}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F4F5870-CBCE-6E49-86D4-A27248FEF2A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{BB86D34F-36D9-1345-8602-5170A8A8DBB9}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja9" sheetId="9" r:id="rId1"/>
+    <sheet name="Hoja8" sheetId="8" r:id="rId2"/>
+    <sheet name="Hoja7" sheetId="7" r:id="rId3"/>
+    <sheet name="Hoja6" sheetId="6" r:id="rId4"/>
+    <sheet name="Hoja5" sheetId="5" r:id="rId5"/>
+    <sheet name="Hoja4" sheetId="4" r:id="rId6"/>
+    <sheet name="Hoja3" sheetId="3" r:id="rId7"/>
+    <sheet name="Hoja2" sheetId="2" r:id="rId8"/>
+    <sheet name="Hoja1" sheetId="1" r:id="rId9"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -35,9 +43,395 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="127">
+  <si>
+    <t>Pruebas cargar_comandos</t>
+  </si>
+  <si>
+    <t>PC01</t>
+  </si>
+  <si>
+    <t>PC02</t>
+  </si>
+  <si>
+    <t>PC03</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Comando</t>
+  </si>
+  <si>
+    <t>Descripcion</t>
+  </si>
+  <si>
+    <t>Resultado Esperado</t>
+  </si>
+  <si>
+    <t>cargar_comandos</t>
+  </si>
+  <si>
+    <t>Cargar archivo válido de comandos</t>
+  </si>
+  <si>
+    <t>Archivo inexistente</t>
+  </si>
+  <si>
+    <t>Archivo vacio</t>
+  </si>
+  <si>
+    <t>cargar_comandos-comandos.txt</t>
+  </si>
+  <si>
+    <t>El sistema carga los comandos correctamente</t>
+  </si>
+  <si>
+    <t>Mensaje de error indicando que el archivo no existe</t>
+  </si>
+  <si>
+    <t>El sistema indica que no hay elementos</t>
+  </si>
+  <si>
+    <t>cargar_elementos</t>
+  </si>
+  <si>
+    <t>cargar_elementos elementos_vacio.txt</t>
+  </si>
+  <si>
+    <t>PE01</t>
+  </si>
+  <si>
+    <t>PE02</t>
+  </si>
+  <si>
+    <t>PE03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comando </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entrada </t>
+  </si>
+  <si>
+    <t>Pruebas cargar_elementos</t>
+  </si>
+  <si>
+    <t>Cargar archivo valido de elementos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Archivo inexistente </t>
+  </si>
+  <si>
+    <t>cargar_elementos elementos.txt</t>
+  </si>
+  <si>
+    <t>cargar_elementos archivo.txt</t>
+  </si>
+  <si>
+    <t>Elementos cargados correctamente</t>
+  </si>
+  <si>
+    <t>Mensaje de error</t>
+  </si>
+  <si>
+    <t>Se indica que no hay elementos</t>
+  </si>
+  <si>
+    <t>Pruebas agregar_movimiento</t>
+  </si>
+  <si>
+    <t>Entrada</t>
+  </si>
+  <si>
+    <t>PM01</t>
+  </si>
+  <si>
+    <t>PM02</t>
+  </si>
+  <si>
+    <t>PM03</t>
+  </si>
+  <si>
+    <t>PM04</t>
+  </si>
+  <si>
+    <t>PM05</t>
+  </si>
+  <si>
+    <t>agregar_movimiento</t>
+  </si>
+  <si>
+    <t>Tipo de movimiento invalido</t>
+  </si>
+  <si>
+    <t>Magnitud negativa</t>
+  </si>
+  <si>
+    <t>Unidad valida diferente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Movimiento valido avanzar </t>
+  </si>
+  <si>
+    <t>Movimiento valido girar</t>
+  </si>
+  <si>
+    <t>agregar_movimiento avanzar 10 m</t>
+  </si>
+  <si>
+    <t>agregar_movimiento girar 90 grd</t>
+  </si>
+  <si>
+    <t>agregar_movimiento volar 10 m</t>
+  </si>
+  <si>
+    <t>agregar_movimiento  avanzar -5 m</t>
+  </si>
+  <si>
+    <t>agregar_movimiento avanzar 1 km</t>
+  </si>
+  <si>
+    <t>Movimiento agregado correctamente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error movimiento invalido </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error magnitud invalida </t>
+  </si>
+  <si>
+    <t>Pruebas agregar_analisis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID </t>
+  </si>
+  <si>
+    <t>Resultado esperado</t>
+  </si>
+  <si>
+    <t>PA01</t>
+  </si>
+  <si>
+    <t>PA02</t>
+  </si>
+  <si>
+    <t>PA03</t>
+  </si>
+  <si>
+    <t>PA04</t>
+  </si>
+  <si>
+    <t>agregar_analisis</t>
+  </si>
+  <si>
+    <t>Analisis fotografiar</t>
+  </si>
+  <si>
+    <t>Analisis composicion</t>
+  </si>
+  <si>
+    <t>Analisis perforar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tipo de analisis invalido </t>
+  </si>
+  <si>
+    <t>agregar_analisis fotografiar roca</t>
+  </si>
+  <si>
+    <t>agregar_analisis composicion duna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">agregar_analisis perforar crater </t>
+  </si>
+  <si>
+    <t>agregar_analisis analizar roca</t>
+  </si>
+  <si>
+    <t>Error</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analisis agregado correctamente </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pruebas agregar_elemento </t>
+  </si>
+  <si>
+    <t>PE04</t>
+  </si>
+  <si>
+    <t>agregar_elemento</t>
+  </si>
+  <si>
+    <t>agregar_elemento roca 5 m 10 20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elemento valido roca </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elemento valido crater </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tipo Invalido </t>
+  </si>
+  <si>
+    <t>agregar_elemento crater 15 m 30 40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">agregar_elemento arbol 10 m 5 6 </t>
+  </si>
+  <si>
+    <t>agregar_elemento duna -5 m 10 20</t>
+  </si>
+  <si>
+    <t>Elemento agregado correctamente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error tipo invalido </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error tamaño invalido </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tamaño negativo </t>
+  </si>
+  <si>
+    <t>Pruebas Guardar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resultado esperado </t>
+  </si>
+  <si>
+    <t>PG01</t>
+  </si>
+  <si>
+    <t>PG02</t>
+  </si>
+  <si>
+    <t>PG03</t>
+  </si>
+  <si>
+    <t>guardar</t>
+  </si>
+  <si>
+    <t>Guardar comandos</t>
+  </si>
+  <si>
+    <t>Guardar elementos</t>
+  </si>
+  <si>
+    <t>guardar comandos salida.txt</t>
+  </si>
+  <si>
+    <t>guardar elementos salida.txt</t>
+  </si>
+  <si>
+    <t>guardar datos salida.txt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Archivo con comandos creado correctamente </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Archivo con elementos creado correctamente </t>
+  </si>
+  <si>
+    <t>Pruebas Simular comandoa</t>
+  </si>
+  <si>
+    <t>PS01</t>
+  </si>
+  <si>
+    <t>PS02</t>
+  </si>
+  <si>
+    <t>PS03</t>
+  </si>
+  <si>
+    <t>simular_comandos</t>
+  </si>
+  <si>
+    <t>Simulacion desde el origen</t>
+  </si>
+  <si>
+    <t>Simulacion desde otra posicion</t>
+  </si>
+  <si>
+    <t>Parametros incompletos</t>
+  </si>
+  <si>
+    <t>simular_comados 0 0</t>
+  </si>
+  <si>
+    <t>simular_comandos 10 5</t>
+  </si>
+  <si>
+    <t>simular_ comandos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se calcula la posicion final </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se calcula nueva posicion final </t>
+  </si>
+  <si>
+    <t>Ayuda</t>
+  </si>
+  <si>
+    <t>PH01</t>
+  </si>
+  <si>
+    <t>PH02</t>
+  </si>
+  <si>
+    <t>PH03</t>
+  </si>
+  <si>
+    <t>ayuda</t>
+  </si>
+  <si>
+    <t>Mostrar todos los comandos</t>
+  </si>
+  <si>
+    <t>Ayuda de un comando</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comando inexistente </t>
+  </si>
+  <si>
+    <t>ayuda agregar_movimiento</t>
+  </si>
+  <si>
+    <t>ayuda comando</t>
+  </si>
+  <si>
+    <t>Lista de comandos disponibles</t>
+  </si>
+  <si>
+    <t>Explicacion del comando</t>
+  </si>
+  <si>
+    <t>Salir</t>
+  </si>
+  <si>
+    <t>comando</t>
+  </si>
+  <si>
+    <t>salir</t>
+  </si>
+  <si>
+    <t>terminar ejecucion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El programa finaliza correctamente </t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -45,16 +439,109 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow (Cuerpo)"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7030A0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00EFAD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFC7D00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2009F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF79FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFE0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -62,18 +549,82 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="Encabezado 1" xfId="1" builtinId="16"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Texto de advertencia" xfId="2" builtinId="11"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFE0000"/>
+      <color rgb="FFAF79FF"/>
+      <color rgb="FFE2009F"/>
+      <color rgb="FFFC7D00"/>
+      <color rgb="FF00EFAD"/>
+      <color rgb="FFFF0000"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -401,10 +952,902 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5844F895-6511-354C-89BB-C96CCAC3B67E}">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="15.33203125" customWidth="1"/>
+    <col min="5" max="5" width="28.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{142D9CCE-CBAD-5C40-B899-2A1659524CE7}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="23" customWidth="1"/>
+    <col min="4" max="4" width="21.5" customWidth="1"/>
+    <col min="5" max="5" width="25.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D4" t="s">
+        <v>118</v>
+      </c>
+      <c r="E4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C5" t="s">
+        <v>117</v>
+      </c>
+      <c r="D5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E06AFE0-2C0E-8B47-80EE-3E98829DE670}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="26.1640625" customWidth="1"/>
+    <col min="4" max="4" width="20.1640625" customWidth="1"/>
+    <col min="5" max="5" width="25.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C5" t="s">
+        <v>104</v>
+      </c>
+      <c r="D5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{790F738B-D871-9B4E-BAE3-2F3AC93878B5}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.33203125" customWidth="1"/>
+    <col min="5" max="5" width="37.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC9B2147-DB08-3E4A-8B7B-32DC57758212}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="15.5" customWidth="1"/>
+    <col min="3" max="3" width="26.6640625" customWidth="1"/>
+    <col min="4" max="4" width="29.5" customWidth="1"/>
+    <col min="5" max="5" width="28.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D6" t="s">
+        <v>79</v>
+      </c>
+      <c r="E6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4960B43E-FD47-D442-8B28-B240A86CA171}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="13.5" customWidth="1"/>
+    <col min="3" max="3" width="19.1640625" customWidth="1"/>
+    <col min="4" max="4" width="28.1640625" customWidth="1"/>
+    <col min="5" max="5" width="26.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AF346BC-E12C-B84C-8120-3314C5E98C75}">
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="18.33203125" customWidth="1"/>
+    <col min="3" max="3" width="23" customWidth="1"/>
+    <col min="4" max="4" width="28.1640625" customWidth="1"/>
+    <col min="5" max="5" width="29.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="21" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+    </row>
+    <row r="2" spans="1:5" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{099F9108-D2C3-734A-BDDE-9FE6C6EEFC66}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="28.33203125" customWidth="1"/>
+    <col min="4" max="4" width="26.1640625" customWidth="1"/>
+    <col min="5" max="5" width="28.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="21" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+    </row>
+    <row r="2" spans="1:5" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E1BA5FA-5B82-1142-B49F-200F0ECA6E42}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="28.1640625" customWidth="1"/>
+    <col min="4" max="4" width="32.6640625" customWidth="1"/>
+    <col min="5" max="5" width="50" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="21" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:5" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>